--- a/data/trans_dic/P3A$otraNOcobra-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,62</t>
+          <t>0,82; 2,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,87</t>
+          <t>0,41; 1,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,95</t>
+          <t>0,78; 1,87</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,51</t>
+          <t>1,06; 3,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,61</t>
+          <t>0,82; 2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,56</t>
+          <t>1,11; 2,58</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,94</t>
+          <t>0,63; 3,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,77</t>
+          <t>2,27; 6,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,92</t>
+          <t>0,96; 3,87</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,55</t>
+          <t>3,36; 5,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,4</t>
+          <t>0,87; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,79</t>
+          <t>2,16; 3,75</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,15</t>
+          <t>2,78; 6,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,0</t>
+          <t>4,04; 7,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,22</t>
+          <t>4,06; 6,29</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 13,56</t>
+          <t>1,03; 13,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 9,58</t>
+          <t>6,71; 9,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,0</t>
+          <t>5,78; 9,54</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,84</t>
+          <t>2,34; 3,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,6</t>
+          <t>3,32; 4,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,0</t>
+          <t>3,07; 4,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4215; 13224</t>
+          <t>4124; 13337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1692; 8344</t>
+          <t>1845; 8246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7249; 18534</t>
+          <t>7384; 17822</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4524; 15868</t>
+          <t>4775; 15505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2849; 9991</t>
+          <t>3135; 10612</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8571; 21391</t>
+          <t>9238; 21559</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4457; 26321</t>
+          <t>4197; 26438</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3733; 11256</t>
+          <t>3768; 11013</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8000; 32731</t>
+          <t>8012; 32286</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35181; 57471</t>
+          <t>34763; 56955</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7328; 23496</t>
+          <t>8503; 23983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42094; 76252</t>
+          <t>43506; 75403</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13966; 29229</t>
+          <t>13220; 28933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34827; 58869</t>
+          <t>33957; 59573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54308; 81903</t>
+          <t>53471; 82738</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2364; 32622</t>
+          <t>2476; 31495</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50932; 72953</t>
+          <t>51060; 72986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58101; 90198</t>
+          <t>57911; 95593</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80038; 129749</t>
+          <t>79145; 129742</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115189; 164650</t>
+          <t>118621; 163864</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>207472; 277744</t>
+          <t>213622; 279212</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraNOcobra-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,64</t>
+          <t>0,81; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,85</t>
+          <t>0,45; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,87</t>
+          <t>0,78; 1,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,43</t>
+          <t>0,97; 3,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,77</t>
+          <t>1,01; 3,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,58</t>
+          <t>1,19; 2,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,96</t>
+          <t>1,8; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,62</t>
+          <t>2,13; 6,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,87</t>
+          <t>2,25; 4,71</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,5</t>
+          <t>3,25; 5,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,45</t>
+          <t>1,45; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,75</t>
+          <t>2,71; 4,09</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,09</t>
+          <t>2,52; 5,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,08</t>
+          <t>5,0; 7,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,29</t>
+          <t>4,25; 6,22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 13,1</t>
+          <t>0,88; 7,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 9,59</t>
+          <t>6,41; 9,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,54</t>
+          <t>5,57; 8,07</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,84</t>
+          <t>2,57; 3,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,58</t>
+          <t>3,75; 4,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 4,02</t>
+          <t>3,32; 4,03</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12966</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4124; 13337</t>
+          <t>4435; 15221</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1845; 8246</t>
+          <t>2210; 9319</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7384; 17822</t>
+          <t>8051; 19985</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>16573</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4775; 15505</t>
+          <t>4694; 16087</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3135; 10612</t>
+          <t>4270; 13627</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9238; 21559</t>
+          <t>10760; 25465</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>21130</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4197; 26438</t>
+          <t>8480; 21378</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3768; 11013</t>
+          <t>3985; 12000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8012; 32286</t>
+          <t>14833; 31001</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>65514</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34763; 56955</t>
+          <t>36753; 60516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8503; 23983</t>
+          <t>12489; 24755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43506; 75403</t>
+          <t>54104; 81470</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48207</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68111</t>
+          <t>71704</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13220; 28933</t>
+          <t>14310; 30687</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33957; 59573</t>
+          <t>41548; 60752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53471; 82738</t>
+          <t>59506; 87056</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>65837</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70934</t>
+          <t>71776</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2476; 31495</t>
+          <t>2081; 16944</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51060; 72986</t>
+          <t>54088; 79196</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57911; 95593</t>
+          <t>60217; 87242</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>104073</t>
+          <t>105619</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>142327</t>
+          <t>154044</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246399</t>
+          <t>259663</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>79145; 129742</t>
+          <t>88466; 124379</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118621; 163864</t>
+          <t>136299; 171876</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213622; 279212</t>
+          <t>234723; 285484</t>
         </is>
       </c>
     </row>
